--- a/Phase2_ISMatch/results/phase2_lc_results.xlsx
+++ b/Phase2_ISMatch/results/phase2_lc_results.xlsx
@@ -16,7 +16,12 @@
     <sheet name="Ranking_Sensitivity_LC" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DeltaTC_Calibration_LC" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="DeltaTC_Convergence_LC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Regulatory_KPIs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sobol_Weights_LC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Stress_Test_LC" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Carbon_Avoided_LC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PROMETHEE_Ranking_LC" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PROMETHEE_Correlation_LC" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Regulatory_KPIs" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -994,6 +999,1234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>S1_conf</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ST_conf</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Y_aggregate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Y_aggregate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0102</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Y_aggregate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8699</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0635</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>top3_stability_pct</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Y is constant; indices undefined (variance=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>top3_stability_pct</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Y is constant; indices undefined (variance=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>top3_stability_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Y is constant; indices undefined (variance=0)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>perturbed_top3</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>top3_unchanged</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>max_rank_shift</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q_demand_peak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Score formula uses DC-side q_norm; plant Q_demand unused</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q_demand_peak</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Score formula uses DC-side q_norm; plant Q_demand unused</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T_required</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T_required</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>distance_km</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>distance_km</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>delta_tc_norm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>delta_tc_norm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[Edge_LC+LowT_60C, Hyperscale_LC+LowT_60C, Mid_LC+LowT_60C]</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>dc_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>shift_pattern</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>annual_hours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ri_temporal_utilization</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Q_recovery_GWh_yr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CO2_avoided_tons_yr</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>equiv_cars_off_road</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>emission_factor_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8760</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5896</v>
+      </c>
+      <c r="G2" t="n">
+        <v>126.54</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34925</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7592.4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>42.3237</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11681.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2539.4</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.6193</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7346.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1597.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mid_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8760</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16.195</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4469.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>971.7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.4056</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1492</v>
+      </c>
+      <c r="I6" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mid_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.4191</v>
+      </c>
+      <c r="H7" t="n">
+        <v>943.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Edge_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8760</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.4783</v>
+      </c>
+      <c r="H8" t="n">
+        <v>684</v>
+      </c>
+      <c r="I8" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Edge_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="H9" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Edge_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="H10" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.276 (gas natural, EU EEA 2024)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank_promethee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phi_net</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_match_rank</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rank_difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mid_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Edge_LC + LowT_60C</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mid_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Edge_LC + MidT_90C</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0776</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2087</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mid_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.3554</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Edge_LC + HighT_130C</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3673</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spearman_rho</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.6667</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.4444</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>n_pair</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>top3_agreement</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>weights_used_promethee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.25, 0.25, 0.25, 0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>weights_used_ismatch</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>beta=0.40, gamma=0.40, delta=0.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>preference_function</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t5 (V-shape with indifference); q=0.01, p=0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ri_temporal, exergy_dt_norm, one_minus_delta_tc, co2_norm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1118,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1175,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1232,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1289,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1346,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1403,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1460,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1517,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1574,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1631,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1688,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1745,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5767</v>
+        <v>0.5723</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1802,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1859,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1916,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5342</v>
+        <v>0.5224</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1973,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2030,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2087,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4702</v>
+        <v>0.4483</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2144,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5766</v>
+        <v>0.5722</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2201,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5766</v>
+        <v>0.5722</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2258,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5766</v>
+        <v>0.5722</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2315,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.534</v>
+        <v>0.5222</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2372,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.534</v>
+        <v>0.5222</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2429,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.534</v>
+        <v>0.5222</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2486,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.47</v>
+        <v>0.4481</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2543,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.47</v>
+        <v>0.4481</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2600,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.47</v>
+        <v>0.4481</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2630,12 +3863,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>pair_id</t>
+          <t>dc_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dc_name</t>
+          <t>dc_q_nominal_kw</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -2650,100 +3883,98 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>dc_q_nominal_kw</t>
+          <t>dc_t_avail_fraction</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>plant_id</t>
+          <t>plant_name</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>process_name</t>
+          <t>plant_description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>plant_tier</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>plant_proximity_band</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>t_req_c</t>
+          <t>plant_t_req_c</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>q_demand_kw</t>
+          <t>plant_q_demand_kw</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>plant_shift_pattern</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>plant_delta_tc_baseline</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>plant_data_source</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>distance_km</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>shift_type</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>t_avail_fraction</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>delta_tc_baseline</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>upgrade_tech_mean</t>
+          <t>RI_quantity</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>upgrade_tech_max</t>
+          <t>RI_temperature</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ri_static</t>
+          <t>RI_availability</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>label_feasible</t>
+          <t>RI_distance</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ri_threshold</t>
+          <t>RI_static</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>source_ref</t>
+          <t>feasible</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P_LC001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>475</v>
       </c>
       <c r="C2" t="n">
         <v>47.6</v>
@@ -2752,83 +3983,77 @@
         <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LowT_01_FoodDry</t>
+          <t>LowT_01_Food_Short</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>food_processing</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fruit/vegetable drying, pasteurisation (Emilia-Romagna)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.92</v>
+        <v>800</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.7334000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7506</v>
-      </c>
-      <c r="S2" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P_LC002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B3" t="n">
+        <v>475</v>
       </c>
       <c r="C3" t="n">
         <v>47.6</v>
@@ -2837,83 +4062,77 @@
         <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LowT_02_Greenhouse</t>
+          <t>LowT_02_Agro_Medium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Heated greenhouse, year-round (Nordic analogue)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>300</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.95</v>
+        <v>1200</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>direct_HX</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7334000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7516</v>
-      </c>
-      <c r="S3" t="b">
-        <v>1</v>
+        <v>0.65</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.625</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / Kalundborg</t>
-        </is>
+        <v>0.4919</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_LC003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>475</v>
       </c>
       <c r="C4" t="n">
         <v>47.6</v>
@@ -2922,83 +4141,77 @@
         <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LowT_03_Aquaculture</t>
+          <t>LowT_03_Dairy_Short</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>aquaculture</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fish farm thermal regulation (ENEA coastal cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>65</v>
       </c>
       <c r="K4" t="n">
-        <v>180</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>650</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0.88</v>
+      <c r="M4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7308</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6473</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6541</v>
-      </c>
-      <c r="S4" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6347</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4</t>
-        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_LC004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B5" t="n">
+        <v>475</v>
       </c>
       <c r="C5" t="n">
         <v>47.6</v>
@@ -3007,83 +4220,77 @@
         <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MidT_04_TextileDye</t>
+          <t>MidT_04_PaperPulp_Medium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>textile</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Textile dyeing/finishing (Prato district, Tuscany)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>800</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2shift</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0.78</v>
+        <v>28127.9</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="S5" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="U5" t="n">
         <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_LC005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B6" t="n">
+        <v>475</v>
       </c>
       <c r="C6" t="n">
         <v>47.6</v>
@@ -3092,83 +4299,77 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MidT_05_WoodDry</t>
+          <t>MidT_05_PaperPulp_Short</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>wood_processing</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Timber kiln drying (Alpine cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K6" t="n">
-        <v>600</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8</v>
+        <v>31141.6</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
+        <v>0.2614</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P_LC006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B7" t="n">
+        <v>475</v>
       </c>
       <c r="C7" t="n">
         <v>47.6</v>
@@ -3177,83 +4378,77 @@
         <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MidT_06_PaperPulp</t>
+          <t>MidT_06_PaperPulp_Long</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>paper_pulp</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paper/pulp pre-drying (Po Valley industrial zone)</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K7" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>21095.9</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>0.85</v>
+      <c r="M7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3756</v>
-      </c>
-      <c r="S7" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P_LC007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B8" t="n">
+        <v>475</v>
       </c>
       <c r="C8" t="n">
         <v>47.6</v>
@@ -3262,83 +4457,77 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HighT_07_Rubber</t>
+          <t>HighT_07_Rubber_Medium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rubber_plastics</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation, moulding (Porto Marghera type)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>130</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>2800</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>2shift</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>0.75</v>
+      <c r="M8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1275</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="S8" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>ENEA B9 / CE-HEAT WP3</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P_LC008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B9" t="n">
+        <v>475</v>
       </c>
       <c r="C9" t="n">
         <v>47.6</v>
@@ -3347,83 +4536,77 @@
         <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HighT_08_ChemReact</t>
+          <t>HighT_08_ChemProcess_Short</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>chemicals</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chemical process reactor pre-heating, solvent recovery</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M9" t="inlineStr">
+        <v>4500</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0.82</v>
+      <c r="M9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1275</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1966</v>
-      </c>
-      <c r="S9" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="U9" t="n">
         <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P_LC009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>Edge_LC</t>
         </is>
+      </c>
+      <c r="B10" t="n">
+        <v>475</v>
       </c>
       <c r="C10" t="n">
         <v>47.6</v>
@@ -3432,83 +4615,77 @@
         <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HighT_09_IndSteam</t>
+          <t>HighT_09_Steam_Long</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>industrial_steam</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Low-pressure industrial steam, autoclave sterilisation</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>135</v>
       </c>
       <c r="K10" t="n">
-        <v>800</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0.7</v>
+        <v>6200</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1125</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2835</v>
-      </c>
-      <c r="S10" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="U10" t="n">
         <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>A9 / CE-HEAT</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_LC010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3104</v>
       </c>
       <c r="C11" t="n">
         <v>47.6</v>
@@ -3517,83 +4694,77 @@
         <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LowT_01_FoodDry</t>
+          <t>LowT_01_Food_Short</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>food_processing</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fruit/vegetable drying, pasteurisation (Emilia-Romagna)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="n">
-        <v>450</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0.92</v>
+        <v>800</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7334000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7506</v>
-      </c>
-      <c r="S11" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7259</v>
+      </c>
+      <c r="U11" t="n">
         <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P_LC011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3104</v>
       </c>
       <c r="C12" t="n">
         <v>47.6</v>
@@ -3602,83 +4773,77 @@
         <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LowT_02_Greenhouse</t>
+          <t>LowT_02_Agro_Medium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Heated greenhouse, year-round (Nordic analogue)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0.95</v>
+        <v>1200</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>direct_HX</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7334000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7516</v>
-      </c>
-      <c r="S12" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="U12" t="n">
         <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / Kalundborg</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P_LC012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3104</v>
       </c>
       <c r="C13" t="n">
         <v>47.6</v>
@@ -3687,83 +4852,77 @@
         <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LowT_03_Aquaculture</t>
+          <t>LowT_03_Dairy_Short</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>aquaculture</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Fish farm thermal regulation (ENEA coastal cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>65</v>
       </c>
       <c r="K13" t="n">
-        <v>180</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>650</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>0.88</v>
+      <c r="M13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6473</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6541</v>
-      </c>
-      <c r="S13" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="U13" t="n">
         <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P_LC013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3104</v>
       </c>
       <c r="C14" t="n">
         <v>47.6</v>
@@ -3772,83 +4931,77 @@
         <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MidT_04_TextileDye</t>
+          <t>MidT_04_PaperPulp_Medium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>textile</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Textile dyeing/finishing (Prato district, Tuscany)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>90</v>
       </c>
       <c r="K14" t="n">
-        <v>800</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2shift</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>0.78</v>
+        <v>28127.9</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5716</v>
-      </c>
-      <c r="S14" t="b">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
+        <v>0.2797</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_LC014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3104</v>
       </c>
       <c r="C15" t="n">
         <v>47.6</v>
@@ -3857,83 +5010,77 @@
         <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MidT_05_WoodDry</t>
+          <t>MidT_05_PaperPulp_Short</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>wood_processing</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Timber kiln drying (Alpine cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K15" t="n">
-        <v>600</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>0.8</v>
+        <v>31141.6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6151</v>
-      </c>
-      <c r="S15" t="b">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
+        <v>0.291</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P_LC015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3104</v>
       </c>
       <c r="C16" t="n">
         <v>47.6</v>
@@ -3942,83 +5089,77 @@
         <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MidT_06_PaperPulp</t>
+          <t>MidT_06_PaperPulp_Long</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>paper_pulp</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Paper/pulp pre-drying (Po Valley industrial zone)</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K16" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>21095.9</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>0.85</v>
+      <c r="M16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3465</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5266</v>
-      </c>
-      <c r="S16" t="b">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
+        <v>0.2626</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P_LC016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3104</v>
       </c>
       <c r="C17" t="n">
         <v>47.6</v>
@@ -4027,83 +5168,77 @@
         <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HighT_07_Rubber</t>
+          <t>HighT_07_Rubber_Medium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>rubber_plastics</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation, moulding (Porto Marghera type)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>130</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>2800</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>2shift</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>0.75</v>
+      <c r="M17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O17" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1275</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4091</v>
-      </c>
-      <c r="S17" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="U17" t="n">
         <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>ENEA B9 / CE-HEAT WP3</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P_LC017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3104</v>
       </c>
       <c r="C18" t="n">
         <v>47.6</v>
@@ -4112,83 +5247,77 @@
         <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HighT_08_ChemReact</t>
+          <t>HighT_08_ChemProcess_Short</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>chemicals</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chemical process reactor pre-heating, solvent recovery</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K18" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>4500</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>0.82</v>
+      <c r="M18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1275</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3991</v>
-      </c>
-      <c r="S18" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="U18" t="n">
         <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P_LC018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
           <t>Mid_LC</t>
         </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3104</v>
       </c>
       <c r="C19" t="n">
         <v>47.6</v>
@@ -4197,836 +5326,778 @@
         <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>3104</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HighT_09_IndSteam</t>
+          <t>HighT_09_Steam_Long</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>industrial_steam</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Low-pressure industrial steam, autoclave sterilisation</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>135</v>
       </c>
       <c r="K19" t="n">
-        <v>800</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>0.7</v>
+        <v>6200</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1125</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3851</v>
-      </c>
-      <c r="S19" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="U19" t="n">
         <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>A9 / CE-HEAT</t>
-        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P_LC019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B20" t="n">
+        <v>24500</v>
       </c>
       <c r="C20" t="n">
         <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E20" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LowT_01_FoodDry</t>
+          <t>LowT_01_Food_Short</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>food_processing</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Fruit/vegetable drying, pasteurisation (Emilia-Romagna)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>60</v>
       </c>
       <c r="K20" t="n">
-        <v>450</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>0.92</v>
+        <v>800</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.7047</v>
       </c>
       <c r="R20" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="S20" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="U20" t="n">
         <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P_LC020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24500</v>
       </c>
       <c r="C21" t="n">
         <v>46</v>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E21" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LowT_02_Greenhouse</t>
+          <t>LowT_02_Agro_Medium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Heated greenhouse, year-round (Nordic analogue)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K21" t="n">
-        <v>300</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>0.95</v>
+        <v>1200</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2shift</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.7047</v>
       </c>
       <c r="R21" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="S21" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / Kalundborg</t>
-        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P_LC021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B22" t="n">
+        <v>24500</v>
       </c>
       <c r="C22" t="n">
         <v>46</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E22" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LowT_03_Aquaculture</t>
+          <t>LowT_03_Dairy_Short</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>aquaculture</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Fish farm thermal regulation (ENEA coastal cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>65</v>
       </c>
       <c r="K22" t="n">
-        <v>180</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M22" t="inlineStr">
+        <v>650</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>0.88</v>
+      <c r="M22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Parametric — ENEA IS benchmark (2021)</t>
+        </is>
       </c>
       <c r="O22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.6219</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6485</v>
-      </c>
-      <c r="S22" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4</t>
-        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_LC022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B23" t="n">
+        <v>24500</v>
       </c>
       <c r="C23" t="n">
         <v>46</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E23" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MidT_04_TextileDye</t>
+          <t>MidT_04_PaperPulp_Medium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>textile</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Textile dyeing/finishing (Prato district, Tuscany)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>90</v>
       </c>
       <c r="K23" t="n">
-        <v>800</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2shift</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>0.78</v>
+        <v>28127.9</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O23" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3329</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="S23" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="U23" t="n">
         <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P_LC023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B24" t="n">
+        <v>24500</v>
       </c>
       <c r="C24" t="n">
         <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E24" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MidT_05_WoodDry</t>
+          <t>MidT_05_PaperPulp_Short</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>wood_processing</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Timber kiln drying (Alpine cluster)</t>
+          <t>short</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>600</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>0.8</v>
+        <v>31141.6</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O24" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7867</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3329</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6095</v>
-      </c>
-      <c r="S24" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="U24" t="n">
         <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_LC024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24500</v>
       </c>
       <c r="C25" t="n">
         <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E25" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MidT_06_PaperPulp</t>
+          <t>MidT_06_PaperPulp_Long</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>paper_pulp</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Paper/pulp pre-drying (Po Valley industrial zone)</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K25" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="inlineStr">
+        <v>21095.9</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>0.85</v>
+      <c r="M25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+        </is>
       </c>
       <c r="O25" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3329</v>
       </c>
       <c r="R25" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="S25" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP3 / ENEA B9</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P_LC025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24500</v>
       </c>
       <c r="C26" t="n">
         <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E26" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HighT_07_Rubber</t>
+          <t>HighT_07_Rubber_Medium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>rubber_plastics</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation, moulding (Porto Marghera type)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>130</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3</v>
-      </c>
-      <c r="M26" t="inlineStr">
+        <v>2800</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>2shift</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>0.75</v>
+      <c r="M26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O26" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.1225</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4035</v>
-      </c>
-      <c r="S26" t="b">
+        <v>0.65</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="U26" t="n">
         <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>ENEA B9 / CE-HEAT WP3</t>
-        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P_LC026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B27" t="n">
+        <v>24500</v>
       </c>
       <c r="C27" t="n">
         <v>46</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E27" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HighT_08_ChemReact</t>
+          <t>HighT_08_ChemProcess_Short</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>chemicals</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chemical process reactor pre-heating, solvent recovery</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K27" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>4500</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>0.82</v>
+      <c r="M27" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1225</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3935</v>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.725</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>CE-HEAT WP4 / ENEA B9</t>
-        </is>
+        <v>0.514</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P_LC027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>Hyperscale_LC</t>
         </is>
+      </c>
+      <c r="B28" t="n">
+        <v>24500</v>
       </c>
       <c r="C28" t="n">
         <v>46</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24500</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HighT_09_IndSteam</t>
+          <t>HighT_09_Steam_Long</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>HighT_130C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>industrial_steam</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Low-pressure industrial steam, autoclave sterilisation</t>
+          <t>long</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>135</v>
       </c>
       <c r="K28" t="n">
-        <v>800</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1shift</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>0.7</v>
+        <v>6200</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+        </is>
       </c>
       <c r="O28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>CO2_HTHP</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1081</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3795</v>
-      </c>
-      <c r="S28" t="b">
+        <v>0.95</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="U28" t="n">
         <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>A9 / CE-HEAT</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -5040,139 +6111,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>process_name</t>
+          <t>dc_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>upgrade_tech_mean</t>
+          <t>tier</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>n_pairs</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ri_mean</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ri_min</t>
+          <t>n_feasible</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ri_max</t>
+          <t>RI_static_mean</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>n_feasible</t>
+          <t>RI_static_max</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>dtc_mean</t>
+          <t>RI_temp_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dist_mean_km</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HighT_130C</t>
+          <t>Edge_LC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CO2_HTHP</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Parametric (ENEA 2021)</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3475</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1966</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4091</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.6347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5733</v>
+        <v>0.7047</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>LowT_60C</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Parametric (ENEA 2021)</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7169</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6485</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7516</v>
+        <v>0.7194</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>0.7289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>0.7047</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Parametric (ENEA 2021)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7084</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>MidT_90C</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5354</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3756</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.6151</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.4167</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="I5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="I6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="I7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Parametric (CE-HEAT WP3/WP4)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="I8" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Parametric (CE-HEAT WP3/WP4)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="I9" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Parametric (CE-HEAT WP3/WP4)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="I10" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -10568,7 +11869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11132,10 +12433,10 @@
         <v>0.7529</v>
       </c>
       <c r="F11" t="n">
-        <v>0.125</v>
+        <v>0.17105</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5548</v>
+        <v>0.5456</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -11184,10 +12485,10 @@
         <v>0.7529</v>
       </c>
       <c r="F12" t="n">
-        <v>0.125</v>
+        <v>0.17105</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5548</v>
+        <v>0.5456</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -11236,10 +12537,10 @@
         <v>0.7583</v>
       </c>
       <c r="F13" t="n">
-        <v>0.125</v>
+        <v>0.17105</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5547</v>
+        <v>0.5455</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -11288,10 +12589,10 @@
         <v>0.7529</v>
       </c>
       <c r="F14" t="n">
-        <v>0.20835</v>
+        <v>0.30307</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4977</v>
+        <v>0.4788</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -11340,10 +12641,10 @@
         <v>0.7529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.20835</v>
+        <v>0.30307</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4977</v>
+        <v>0.4788</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -11392,10 +12693,10 @@
         <v>0.7583</v>
       </c>
       <c r="F16" t="n">
-        <v>0.20835</v>
+        <v>0.30307</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4975</v>
+        <v>0.4785</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -11444,10 +12745,10 @@
         <v>0.7529</v>
       </c>
       <c r="F17" t="n">
-        <v>0.28665</v>
+        <v>0.43571</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4201</v>
+        <v>0.3903</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -11496,10 +12797,10 @@
         <v>0.7529</v>
       </c>
       <c r="F18" t="n">
-        <v>0.28665</v>
+        <v>0.43571</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4201</v>
+        <v>0.3903</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -11548,10 +12849,10 @@
         <v>0.7583</v>
       </c>
       <c r="F19" t="n">
-        <v>0.28665</v>
+        <v>0.43571</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4198</v>
+        <v>0.39</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -11600,10 +12901,10 @@
         <v>0.7529</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0625</v>
+        <v>0.11703</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5673</v>
+        <v>0.5564</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -11652,10 +12953,10 @@
         <v>0.7529</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0625</v>
+        <v>0.11703</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5673</v>
+        <v>0.5564</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -11704,10 +13005,10 @@
         <v>0.7583</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0625</v>
+        <v>0.11703</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5672</v>
+        <v>0.5563</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -11756,10 +13057,10 @@
         <v>0.7529</v>
       </c>
       <c r="F23" t="n">
-        <v>0.10418</v>
+        <v>0.22042</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4953</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -11808,10 +13109,10 @@
         <v>0.7529</v>
       </c>
       <c r="F24" t="n">
-        <v>0.10418</v>
+        <v>0.22042</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4953</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -11860,10 +13161,10 @@
         <v>0.7583</v>
       </c>
       <c r="F25" t="n">
-        <v>0.10418</v>
+        <v>0.22042</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5183</v>
+        <v>0.4951</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -11912,10 +13213,10 @@
         <v>0.7529</v>
       </c>
       <c r="F26" t="n">
-        <v>0.14333</v>
+        <v>0.33114</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4487</v>
+        <v>0.4112</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -11964,10 +13265,10 @@
         <v>0.7529</v>
       </c>
       <c r="F27" t="n">
-        <v>0.14333</v>
+        <v>0.33114</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4487</v>
+        <v>0.4112</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -12016,10 +13317,10 @@
         <v>0.7583</v>
       </c>
       <c r="F28" t="n">
-        <v>0.14333</v>
+        <v>0.33114</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4485</v>
+        <v>0.4109</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -12068,10 +13369,10 @@
         <v>0.7529</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03125</v>
+        <v>0.08007</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5736</v>
+        <v>0.5638</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -12120,10 +13421,10 @@
         <v>0.7529</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03125</v>
+        <v>0.08007</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5736</v>
+        <v>0.5638</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -12172,10 +13473,10 @@
         <v>0.7583</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03125</v>
+        <v>0.08007</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5735</v>
+        <v>0.5637</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -12224,10 +13525,10 @@
         <v>0.7529</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05209</v>
+        <v>0.16031</v>
       </c>
       <c r="G32" t="n">
-        <v>0.529</v>
+        <v>0.5073</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -12276,10 +13577,10 @@
         <v>0.7529</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05209</v>
+        <v>0.16031</v>
       </c>
       <c r="G33" t="n">
-        <v>0.529</v>
+        <v>0.5073</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -12328,10 +13629,10 @@
         <v>0.7583</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05209</v>
+        <v>0.16031</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5071</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -12380,10 +13681,10 @@
         <v>0.7529</v>
       </c>
       <c r="F35" t="n">
-        <v>0.07167</v>
+        <v>0.25167</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4631</v>
+        <v>0.4271</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -12432,10 +13733,10 @@
         <v>0.7529</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07167</v>
+        <v>0.25167</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4631</v>
+        <v>0.4271</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12484,10 +13785,10 @@
         <v>0.7583</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07167</v>
+        <v>0.25167</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4628</v>
+        <v>0.4268</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12536,10 +13837,10 @@
         <v>0.7529</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01562</v>
+        <v>0.05478</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5767</v>
+        <v>0.5688</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -12588,10 +13889,10 @@
         <v>0.7529</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01562</v>
+        <v>0.05478</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5767</v>
+        <v>0.5688</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12640,10 +13941,10 @@
         <v>0.7583</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01562</v>
+        <v>0.05478</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5766</v>
+        <v>0.5688</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12692,10 +13993,10 @@
         <v>0.7529</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02604</v>
+        <v>0.11659</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5342</v>
+        <v>0.5161</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12744,10 +14045,10 @@
         <v>0.7529</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02604</v>
+        <v>0.11659</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5342</v>
+        <v>0.5161</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -12796,10 +14097,10 @@
         <v>0.7583</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02604</v>
+        <v>0.11659</v>
       </c>
       <c r="G43" t="n">
-        <v>0.534</v>
+        <v>0.5158</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -12848,10 +14149,10 @@
         <v>0.7529</v>
       </c>
       <c r="F44" t="n">
-        <v>0.03583</v>
+        <v>0.19127</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4702</v>
+        <v>0.4391</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12900,10 +14201,10 @@
         <v>0.7529</v>
       </c>
       <c r="F45" t="n">
-        <v>0.03583</v>
+        <v>0.19127</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4702</v>
+        <v>0.4391</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12952,10 +14253,10 @@
         <v>0.7583</v>
       </c>
       <c r="F46" t="n">
-        <v>0.03583</v>
+        <v>0.19127</v>
       </c>
       <c r="G46" t="n">
-        <v>0.47</v>
+        <v>0.4389</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -12981,6 +14282,474 @@
       </c>
       <c r="N46" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.03748</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>35040</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.03748</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>35040</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LowT_60C</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.03748</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>35040</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MidT_90C</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.5896</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5222</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Edge_LC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mid_LC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hyperscale_LC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HighT_130C</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>per_scenario</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12994,7 +14763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13034,10 +14803,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0573</v>
+        <v>0.0275</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04131</v>
+        <v>0.022</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -13056,10 +14825,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0287</v>
+        <v>0.0209</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02067</v>
+        <v>0.01608</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -13078,10 +14847,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0144</v>
+        <v>0.0159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01036</v>
+        <v>0.01177</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -13100,18 +14869,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0072</v>
+        <v>0.0121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00516</v>
+        <v>0.00861</v>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00633</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>

--- a/Phase2_ISMatch/results/phase2_lc_results.xlsx
+++ b/Phase2_ISMatch/results/phase2_lc_results.xlsx
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0141</v>
+        <v>0.017</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0137</v>
+        <v>0.0144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0274</v>
+        <v>0.03</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="3">
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0276</v>
+        <v>0.0268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1054</v>
+        <v>0.0993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0102</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="4">
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8699</v>
+        <v>0.8734</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0701</v>
+        <v>0.0702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.887</v>
+        <v>0.8905</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0635</v>
+        <v>0.0636</v>
       </c>
     </row>
     <row r="5">
@@ -1529,16 +1529,16 @@
         <v>8760</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="G2" t="n">
-        <v>126.54</v>
+        <v>125.7673</v>
       </c>
       <c r="H2" t="n">
-        <v>34925</v>
+        <v>34711.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7592.4</v>
+        <v>7546</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1571,16 +1571,16 @@
         <v>2500</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="G3" t="n">
-        <v>42.3237</v>
+        <v>45.0677</v>
       </c>
       <c r="H3" t="n">
-        <v>11681.4</v>
+        <v>12438.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2539.4</v>
+        <v>2704.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1613,16 +1613,16 @@
         <v>2500</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="G4" t="n">
-        <v>26.6193</v>
+        <v>27.538</v>
       </c>
       <c r="H4" t="n">
-        <v>7346.9</v>
+        <v>7600.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1597.2</v>
+        <v>1652.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1655,16 +1655,16 @@
         <v>8760</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="G5" t="n">
-        <v>16.195</v>
+        <v>16.0862</v>
       </c>
       <c r="H5" t="n">
-        <v>4469.8</v>
+        <v>4439.8</v>
       </c>
       <c r="I5" t="n">
-        <v>971.7</v>
+        <v>965.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1697,16 +1697,16 @@
         <v>2500</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4056</v>
+        <v>5.7571</v>
       </c>
       <c r="H6" t="n">
-        <v>1492</v>
+        <v>1589</v>
       </c>
       <c r="I6" t="n">
-        <v>324.3</v>
+        <v>345.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1739,16 +1739,16 @@
         <v>2500</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4191</v>
+        <v>3.5355</v>
       </c>
       <c r="H7" t="n">
-        <v>943.7</v>
+        <v>975.8</v>
       </c>
       <c r="I7" t="n">
-        <v>205.1</v>
+        <v>212.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
         <v>8760</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4783</v>
+        <v>2.4616</v>
       </c>
       <c r="H8" t="n">
-        <v>684</v>
+        <v>679.4</v>
       </c>
       <c r="I8" t="n">
-        <v>148.7</v>
+        <v>147.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1823,16 +1823,16 @@
         <v>2500</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8272</v>
+        <v>0.881</v>
       </c>
       <c r="H9" t="n">
-        <v>228.3</v>
+        <v>243.2</v>
       </c>
       <c r="I9" t="n">
-        <v>49.6</v>
+        <v>52.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         <v>2500</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5232</v>
+        <v>0.541</v>
       </c>
       <c r="H10" t="n">
-        <v>144.4</v>
+        <v>149.3</v>
       </c>
       <c r="I10" t="n">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4086</v>
+        <v>0.4412</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2616</v>
+        <v>0.2366</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1759</v>
+        <v>0.2037</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.155</v>
+        <v>0.1817</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.008</v>
+        <v>-0.0213</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.0776</v>
+        <v>-0.1042</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2079</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.3554</v>
+        <v>-0.3587</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.3673</v>
+        <v>-0.3711</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5723</v>
+        <v>0.5904</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5224</v>
+        <v>0.5206</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4483</v>
+        <v>0.4542</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5722</v>
+        <v>0.5901</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5722</v>
+        <v>0.5901</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5722</v>
+        <v>0.5901</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5222</v>
+        <v>0.5205</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5222</v>
+        <v>0.5205</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5222</v>
+        <v>0.5205</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4481</v>
+        <v>0.4539</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4481</v>
+        <v>0.4539</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4481</v>
+        <v>0.4539</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+          <t>Food drying - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+          <t>Agro-industrial processing - medium proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+          <t>Dairy processing - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - medium proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - short proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - long proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+          <t>Rubber vulcanisation - medium proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+          <t>Chemical process - short proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+          <t>Industrial steam - long proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+          <t>Food drying - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+          <t>Agro-industrial processing - medium proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+          <t>Dairy processing - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - medium proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - short proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - long proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+          <t>Rubber vulcanisation - medium proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+          <t>Chemical process - short proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+          <t>Industrial steam - long proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Food drying — short proximity scenario [parametric, ENEA]</t>
+          <t>Food drying - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Agro-industrial processing — medium proximity scenario [parametric, ENEA]</t>
+          <t>Agro-industrial processing - medium proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dairy processing — short proximity scenario [parametric, ENEA]</t>
+          <t>Dairy processing - short proximity scenario [parametric, ENEA]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Parametric — ENEA IS benchmark (2021)</t>
+          <t>Parametric - ENEA IS benchmark (2021)</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — medium proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - medium proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — short proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - short proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Paper/pulp mill — long proximity [parametric, Hotmaps-informed]</t>
+          <t>Paper/pulp mill - long proximity [parametric, Hotmaps-informed]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
+          <t>Parametric - Hotmaps EU Paper statistics [Manz &amp; Fleiter 2018, DOI:10.5281/zenodo.4687147]; T-profile: Fleiter et al. (2013)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rubber vulcanisation — medium proximity [parametric, CE-HEAT]</t>
+          <t>Rubber vulcanisation - medium proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chemical process — short proximity [parametric, CE-HEAT]</t>
+          <t>Chemical process - short proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Industrial steam — long proximity [parametric, CE-HEAT]</t>
+          <t>Industrial steam - long proximity [parametric, CE-HEAT]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Parametric — CE-HEAT taxonomy (WP3/WP4)</t>
+          <t>Parametric - CE-HEAT taxonomy (WP3/WP4)</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+          <t>Parametric - Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+          <t>Parametric - Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Parametric — Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
+          <t>Parametric - Hotmaps-informed (Manz &amp; Fleiter 2018)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -6487,7 +6487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6528,30 +6528,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>is_match_score_raw</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gamma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>n_weighted_steps</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>exergy_norm_method</t>
         </is>
@@ -6572,7 +6577,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E2" t="n">
         <v>0.7529</v>
@@ -6581,26 +6586,29 @@
         <v>0.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5298</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0.4</v>
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>0.4</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L2" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6621,7 +6629,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E3" t="n">
         <v>0.7529</v>
@@ -6630,26 +6638,29 @@
         <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5298</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J3" t="n">
         <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6670,7 +6681,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E4" t="n">
         <v>0.7583</v>
@@ -6679,26 +6690,29 @@
         <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5296999999999999</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.5476</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L4" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6719,35 +6733,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E5" t="n">
         <v>0.7529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4561</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.4532</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J5" t="n">
         <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L5" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6768,35 +6785,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E6" t="n">
         <v>0.7529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4561</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.4532</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L6" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6817,35 +6837,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E7" t="n">
         <v>0.7583</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4558</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.4531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L7" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6866,35 +6889,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E8" t="n">
         <v>0.7529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3628</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4</v>
+        <v>0.3681</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J8" t="n">
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>16704</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6915,35 +6941,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E9" t="n">
         <v>0.7529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3628</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.4</v>
+        <v>0.3681</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
         <v>16704</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -6964,35 +6993,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E10" t="n">
         <v>0.7583</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3625</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4</v>
+        <v>0.3678</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J10" t="n">
         <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
         <v>16704</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
@@ -7099,7 +7131,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1399</v>
+        <v>0.149</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7128,7 +7160,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.0197</v>
+        <v>0.0149</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7186,7 +7218,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1399</v>
+        <v>0.149</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7215,7 +7247,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.0197</v>
+        <v>0.0149</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7273,7 +7305,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1399</v>
+        <v>0.1488</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7302,7 +7334,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.0196</v>
+        <v>0.0149</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7331,7 +7363,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.0273</v>
+        <v>0.0287</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7360,7 +7392,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2402</v>
+        <v>0.2493</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -7389,7 +7421,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1367</v>
+        <v>0.1325</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -7418,7 +7450,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.0273</v>
+        <v>0.0287</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -7447,7 +7479,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.2402</v>
+        <v>0.2493</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -7476,7 +7508,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1367</v>
+        <v>0.1325</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -7505,7 +7537,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.0277</v>
+        <v>0.0291</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7534,7 +7566,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.2407</v>
+        <v>0.2497</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -7563,7 +7595,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1371</v>
+        <v>0.133</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -7592,7 +7624,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.16</v>
+        <v>0.1616</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7621,7 +7653,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.3405</v>
+        <v>0.3496</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7650,7 +7682,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.2536</v>
+        <v>0.2502</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -7679,7 +7711,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.16</v>
+        <v>0.1616</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7708,7 +7740,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.3405</v>
+        <v>0.3496</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7737,7 +7769,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.2536</v>
+        <v>0.2502</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -7766,7 +7798,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.1609</v>
+        <v>0.1626</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -7795,7 +7827,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.3415</v>
+        <v>0.3505</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -7824,7 +7856,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.2546</v>
+        <v>0.2512</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -7853,7 +7885,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.2926</v>
+        <v>0.2946</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -7882,7 +7914,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.4408</v>
+        <v>0.4498</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -7911,7 +7943,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.3706</v>
+        <v>0.3678</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -7940,7 +7972,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.2926</v>
+        <v>0.2946</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -7969,7 +8001,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.4408</v>
+        <v>0.4498</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -7998,7 +8030,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.3706</v>
+        <v>0.3678</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -8027,7 +8059,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.2941</v>
+        <v>0.2961</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -8056,7 +8088,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.4424</v>
+        <v>0.4513</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -8085,7 +8117,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.3721</v>
+        <v>0.3694</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -8143,7 +8175,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.2346</v>
+        <v>0.2482</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -8172,7 +8204,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.1209</v>
+        <v>0.1164</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -8230,7 +8262,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.2346</v>
+        <v>0.2482</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -8259,7 +8291,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.1209</v>
+        <v>0.1164</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -8317,7 +8349,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.234</v>
+        <v>0.2474</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -8346,7 +8378,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.1202</v>
+        <v>0.1158</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -8375,7 +8407,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.1287</v>
+        <v>0.1319</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -8404,7 +8436,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.3349</v>
+        <v>0.3484</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -8433,7 +8465,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.2379</v>
+        <v>0.234</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -8462,7 +8494,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.1287</v>
+        <v>0.1319</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -8491,7 +8523,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.3349</v>
+        <v>0.3484</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8520,7 +8552,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.2379</v>
+        <v>0.234</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8549,7 +8581,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.1285</v>
+        <v>0.1317</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8578,7 +8610,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.3348</v>
+        <v>0.3482</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8607,7 +8639,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.2377</v>
+        <v>0.234</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8636,7 +8668,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.2614</v>
+        <v>0.2649</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8665,7 +8697,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.4352</v>
+        <v>0.4487</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -8694,7 +8726,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.3549</v>
+        <v>0.3517</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -8723,7 +8755,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.2614</v>
+        <v>0.2649</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8752,7 +8784,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.4352</v>
+        <v>0.4487</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8781,7 +8813,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.3549</v>
+        <v>0.3517</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -8810,7 +8842,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.2617</v>
+        <v>0.2652</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -8839,7 +8871,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.4356</v>
+        <v>0.4491</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -8868,7 +8900,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.3552</v>
+        <v>0.3521</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8897,7 +8929,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.394</v>
+        <v>0.3978</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8926,7 +8958,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.5355</v>
+        <v>0.549</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8955,7 +8987,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.4718</v>
+        <v>0.4693</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8984,7 +9016,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.394</v>
+        <v>0.3978</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -9013,7 +9045,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.5355</v>
+        <v>0.549</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -9042,7 +9074,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.4718</v>
+        <v>0.4693</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -9071,7 +9103,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.3949</v>
+        <v>0.3987</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -9100,7 +9132,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.5365</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -9129,7 +9161,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.4727</v>
+        <v>0.4703</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -9158,7 +9190,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.0975</v>
+        <v>0.1022</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9187,7 +9219,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.3292</v>
+        <v>0.3473</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9216,7 +9248,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.2222</v>
+        <v>0.2179</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9245,7 +9277,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.0975</v>
+        <v>0.1022</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9274,7 +9306,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.3292</v>
+        <v>0.3473</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9303,7 +9335,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.2222</v>
+        <v>0.2179</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9332,7 +9364,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1008</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9361,7 +9393,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.3281</v>
+        <v>0.346</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9390,7 +9422,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.2208</v>
+        <v>0.2167</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9419,7 +9451,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.2301</v>
+        <v>0.2351</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9448,7 +9480,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.4295</v>
+        <v>0.4476</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -9477,7 +9509,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.3391</v>
+        <v>0.3355</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -9506,7 +9538,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.2301</v>
+        <v>0.2351</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -9535,7 +9567,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.4295</v>
+        <v>0.4476</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -9564,7 +9596,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.3391</v>
+        <v>0.3355</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -9593,7 +9625,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.2293</v>
+        <v>0.2343</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -9622,7 +9654,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.4289</v>
+        <v>0.4468</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -9651,7 +9683,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.3383</v>
+        <v>0.3349</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -9680,7 +9712,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.3628</v>
+        <v>0.3681</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -9709,7 +9741,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.5298</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -9738,7 +9770,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.4561</v>
+        <v>0.4532</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -9767,7 +9799,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.3628</v>
+        <v>0.3681</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -9796,7 +9828,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.5298</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -9825,7 +9857,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.4561</v>
+        <v>0.4532</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -9854,7 +9886,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.3625</v>
+        <v>0.3678</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -9883,7 +9915,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -9912,7 +9944,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.4558</v>
+        <v>0.4531</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -9941,7 +9973,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.4954</v>
+        <v>0.5011</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -9970,7 +10002,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.6301</v>
+        <v>0.6482</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -9999,7 +10031,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5708</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -10028,7 +10060,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.4954</v>
+        <v>0.5011</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -10057,7 +10089,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.6301</v>
+        <v>0.6482</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -10086,7 +10118,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5708</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -10115,7 +10147,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.4956</v>
+        <v>0.5013</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -10144,7 +10176,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.6306</v>
+        <v>0.6485</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -10173,7 +10205,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.5733</v>
+        <v>0.5712</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -10202,7 +10234,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.1989</v>
+        <v>0.2054</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -10231,7 +10263,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.4239</v>
+        <v>0.4465</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -10260,7 +10292,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.3234</v>
+        <v>0.3194</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -10289,7 +10321,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.1989</v>
+        <v>0.2054</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -10318,7 +10350,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.4239</v>
+        <v>0.4465</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -10347,7 +10379,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.3234</v>
+        <v>0.3194</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -10376,7 +10408,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.1969</v>
+        <v>0.2034</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -10405,7 +10437,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.4222</v>
+        <v>0.4446</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -10434,7 +10466,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.3214</v>
+        <v>0.3177</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -10463,7 +10495,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.3315</v>
+        <v>0.3384</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -10492,7 +10524,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.5242</v>
+        <v>0.5468</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -10521,7 +10553,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.4404</v>
+        <v>0.437</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -10550,7 +10582,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.3315</v>
+        <v>0.3384</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -10579,7 +10611,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.5242</v>
+        <v>0.5468</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -10608,7 +10640,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.4404</v>
+        <v>0.437</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -10637,7 +10669,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.3301</v>
+        <v>0.3369</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -10666,7 +10698,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.523</v>
+        <v>0.5454</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -10695,7 +10727,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.4389</v>
+        <v>0.4358</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -10724,7 +10756,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.4642</v>
+        <v>0.4713</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -10753,7 +10785,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6471</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -10782,7 +10814,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.5573</v>
+        <v>0.5547</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -10811,7 +10843,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.4642</v>
+        <v>0.4713</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -10840,7 +10872,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6471</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -10869,7 +10901,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.5573</v>
+        <v>0.5547</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -10898,7 +10930,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.4633</v>
+        <v>0.4704</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -10927,7 +10959,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.6238</v>
+        <v>0.6462</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10956,7 +10988,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.5564</v>
+        <v>0.554</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -10985,11 +11017,11 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.5968</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>high_priority</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11046,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.7248</v>
+        <v>0.7474</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -11043,7 +11075,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.6743</v>
+        <v>0.6723</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -11072,11 +11104,11 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.5968</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>high_priority</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11133,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.7248</v>
+        <v>0.7474</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11130,7 +11162,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.6743</v>
+        <v>0.6723</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -11159,11 +11191,11 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.5964</v>
+        <v>0.6039</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>high_priority</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11220,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.7247</v>
+        <v>0.7471</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11217,7 +11249,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6722</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -11247,12 +11279,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dc_name</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ndcg_at_k</t>
+          <t>ndcg_at_9</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -11272,7 +11304,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ri_gt05_rate_pct</t>
+          <t>n_pairs</t>
         </is>
       </c>
     </row>
@@ -11288,19 +11320,19 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3333</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>44.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -11315,19 +11347,19 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>0.9881</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3333</v>
       </c>
       <c r="E3" t="n">
         <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>66.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -11342,19 +11374,19 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="D4" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3333</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>66.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -11365,29 +11397,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>ALL_pooled</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.9759</v>
       </c>
       <c r="D5" t="n">
         <v>0.3333</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>59.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RI_static_baseline</t>
+          <t>RI_temporal_baseline</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11396,25 +11428,25 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.3333</v>
-      </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>44.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RI_static_baseline</t>
+          <t>RI_temporal_baseline</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11423,25 +11455,25 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.3333</v>
-      </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>66.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RI_static_baseline</t>
+          <t>RI_temporal_baseline</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11450,46 +11482,46 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.3333</v>
-      </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>66.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RI_static_baseline</t>
+          <t>RI_temporal_baseline</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>ALL_pooled</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9711</v>
       </c>
       <c r="D9" t="n">
         <v>0.3333</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>59.3</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11549,13 +11581,13 @@
         <v>0.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4729</v>
+        <v>0.997</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3314</v>
+        <v>0.9917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -11569,13 +11601,13 @@
         <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4729</v>
+        <v>0.9956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3314</v>
+        <v>0.9886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5454</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -11589,173 +11621,173 @@
         <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4729</v>
+        <v>0.9956</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3314</v>
+        <v>0.9886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5454</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="B5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.3</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.4729</v>
+        <v>0.9956</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3314</v>
+        <v>0.9886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5454</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4729</v>
+        <v>0.9917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5454</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4729</v>
+        <v>0.9917</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3314</v>
+        <v>0.9878</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5454</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B8" t="n">
         <v>0.3</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.4</v>
-      </c>
       <c r="C8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4729</v>
+        <v>0.9917</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3314</v>
+        <v>0.9878</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5454</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="B9" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="n">
         <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C11" t="n">
         <v>0.3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C12" t="n">
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="13">
@@ -11763,39 +11795,39 @@
         <v>0.4</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C14" t="n">
         <v>0.3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="15">
@@ -11803,19 +11835,19 @@
         <v>0.5</v>
       </c>
       <c r="B15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C15" t="n">
         <v>0.3</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.2</v>
-      </c>
       <c r="D15" t="n">
-        <v>0.4729</v>
+        <v>0.9915</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3314</v>
+        <v>0.9881</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5454</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="16">
@@ -11829,13 +11861,13 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4729</v>
+        <v>0.9871</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3314</v>
+        <v>0.9778</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5454</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="17">
@@ -11849,13 +11881,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4729</v>
+        <v>0.9871</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3314</v>
+        <v>0.9778</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5454</v>
+        <v>0.9971</v>
       </c>
     </row>
   </sheetData>
@@ -11869,7 +11901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11910,35 +11942,40 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>is_match_score_raw</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gamma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>n_weighted_steps</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>exergy_norm_method</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>iteration</t>
         </is>
@@ -11959,7 +11996,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E2" t="n">
         <v>0.7529</v>
@@ -11968,31 +12005,34 @@
         <v>0.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5298</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0.4</v>
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>0.4</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L2" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12011,7 +12051,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E3" t="n">
         <v>0.7529</v>
@@ -12020,31 +12060,34 @@
         <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5298</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J3" t="n">
         <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12063,7 +12106,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E4" t="n">
         <v>0.7583</v>
@@ -12072,31 +12115,34 @@
         <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5296999999999999</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.5476</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J4" t="n">
         <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L4" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12115,40 +12161,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E5" t="n">
         <v>0.7529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4561</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.4532</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J5" t="n">
         <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L5" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12167,40 +12216,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E6" t="n">
         <v>0.7529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4561</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.4532</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L6" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12219,40 +12271,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E7" t="n">
         <v>0.7583</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4558</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.4531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L7" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12271,40 +12326,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E8" t="n">
         <v>0.7529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3628</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4</v>
+        <v>0.3681</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J8" t="n">
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>16704</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12323,40 +12381,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E9" t="n">
         <v>0.7529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3628</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.4</v>
+        <v>0.3681</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J9" t="n">
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
         <v>16704</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12375,40 +12436,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E10" t="n">
         <v>0.7583</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5733</v>
+        <v>0.5767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3625</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4</v>
+        <v>0.3678</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J10" t="n">
         <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
         <v>16704</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12427,7 +12491,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E11" t="n">
         <v>0.7529</v>
@@ -12436,31 +12500,34 @@
         <v>0.17105</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5456</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.5637</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L11" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M11" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12479,7 +12546,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E12" t="n">
         <v>0.7529</v>
@@ -12488,31 +12555,34 @@
         <v>0.17105</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5456</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.5637</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J12" t="n">
         <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L12" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12531,7 +12601,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E13" t="n">
         <v>0.7583</v>
@@ -12540,31 +12610,34 @@
         <v>0.17105</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4</v>
+        <v>0.5634</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L13" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12583,40 +12656,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E14" t="n">
         <v>0.7529</v>
       </c>
       <c r="F14" t="n">
-        <v>0.30307</v>
+        <v>0.30787</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4788</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4</v>
+        <v>0.4762</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J14" t="n">
         <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L14" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12635,40 +12711,43 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E15" t="n">
         <v>0.7529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.30307</v>
+        <v>0.30787</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4788</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.4762</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J15" t="n">
         <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L15" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M15" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12687,40 +12766,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E16" t="n">
         <v>0.7583</v>
       </c>
       <c r="F16" t="n">
-        <v>0.30307</v>
+        <v>0.30787</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4785</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4</v>
+        <v>0.4761</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L16" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12739,40 +12821,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E17" t="n">
         <v>0.7529</v>
       </c>
       <c r="F17" t="n">
-        <v>0.43571</v>
+        <v>0.43829</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3903</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.4</v>
+        <v>0.3957</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J17" t="n">
         <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M17" t="n">
         <v>16704</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12791,40 +12876,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E18" t="n">
         <v>0.7529</v>
       </c>
       <c r="F18" t="n">
-        <v>0.43571</v>
+        <v>0.43829</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3903</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.4</v>
+        <v>0.3957</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J18" t="n">
         <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
         <v>16704</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12843,40 +12931,43 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E19" t="n">
         <v>0.7583</v>
       </c>
       <c r="F19" t="n">
-        <v>0.43571</v>
+        <v>0.43829</v>
       </c>
       <c r="G19" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.3955</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J19" t="n">
         <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="n">
         <v>16704</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12895,7 +12986,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E20" t="n">
         <v>0.7529</v>
@@ -12904,31 +12995,34 @@
         <v>0.11703</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5564</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.5745</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J20" t="n">
         <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L20" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12947,7 +13041,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E21" t="n">
         <v>0.7529</v>
@@ -12956,31 +13050,34 @@
         <v>0.11703</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5564</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.4</v>
+        <v>0.5745</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J21" t="n">
         <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L21" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12999,7 +13096,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E22" t="n">
         <v>0.7583</v>
@@ -13008,31 +13105,34 @@
         <v>0.11703</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5563</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.4</v>
+        <v>0.5742</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J22" t="n">
         <v>0.4</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L22" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M22" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13051,40 +13151,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E23" t="n">
         <v>0.7529</v>
       </c>
       <c r="F23" t="n">
-        <v>0.22042</v>
+        <v>0.22391</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4953</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.493</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J23" t="n">
         <v>0.4</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L23" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M23" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13103,40 +13206,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E24" t="n">
         <v>0.7529</v>
       </c>
       <c r="F24" t="n">
-        <v>0.22042</v>
+        <v>0.22391</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4953</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4</v>
+        <v>0.493</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J24" t="n">
         <v>0.4</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L24" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13155,40 +13261,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E25" t="n">
         <v>0.7583</v>
       </c>
       <c r="F25" t="n">
-        <v>0.22042</v>
+        <v>0.22391</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4951</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.4929</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J25" t="n">
         <v>0.4</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L25" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M25" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13207,40 +13316,43 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E26" t="n">
         <v>0.7529</v>
       </c>
       <c r="F26" t="n">
-        <v>0.33114</v>
+        <v>0.3331</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4112</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.4168</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J26" t="n">
         <v>0.4</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="n">
         <v>16704</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13259,40 +13371,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E27" t="n">
         <v>0.7529</v>
       </c>
       <c r="F27" t="n">
-        <v>0.33114</v>
+        <v>0.3331</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4112</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.4168</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J27" t="n">
         <v>0.4</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" t="n">
         <v>16704</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13311,40 +13426,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E28" t="n">
         <v>0.7583</v>
       </c>
       <c r="F28" t="n">
-        <v>0.33114</v>
+        <v>0.3331</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4109</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.4</v>
+        <v>0.4165</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J28" t="n">
         <v>0.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
         <v>16704</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13363,7 +13481,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E29" t="n">
         <v>0.7529</v>
@@ -13372,31 +13490,34 @@
         <v>0.08007</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5638</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.4</v>
+        <v>0.5819</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J29" t="n">
         <v>0.4</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M29" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13415,7 +13536,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E30" t="n">
         <v>0.7529</v>
@@ -13424,31 +13545,34 @@
         <v>0.08007</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5638</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.5819</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J30" t="n">
         <v>0.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L30" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M30" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13467,7 +13591,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E31" t="n">
         <v>0.7583</v>
@@ -13476,31 +13600,34 @@
         <v>0.08007</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5637</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.5816</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J31" t="n">
         <v>0.4</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L31" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M31" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13519,40 +13646,43 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E32" t="n">
         <v>0.7529</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16031</v>
+        <v>0.16285</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5073</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.5052</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J32" t="n">
         <v>0.4</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L32" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M32" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13571,40 +13701,43 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E33" t="n">
         <v>0.7529</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16031</v>
+        <v>0.16285</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5073</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0.4</v>
+        <v>0.5052</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J33" t="n">
         <v>0.4</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M33" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13623,40 +13756,43 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E34" t="n">
         <v>0.7583</v>
       </c>
       <c r="F34" t="n">
-        <v>0.16031</v>
+        <v>0.16285</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5071</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.5052</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J34" t="n">
         <v>0.4</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L34" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M34" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13675,40 +13811,43 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E35" t="n">
         <v>0.7529</v>
       </c>
       <c r="F35" t="n">
-        <v>0.25167</v>
+        <v>0.25316</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4271</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.4328</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J35" t="n">
         <v>0.4</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" t="n">
         <v>16704</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13727,40 +13866,43 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E36" t="n">
         <v>0.7529</v>
       </c>
       <c r="F36" t="n">
-        <v>0.25167</v>
+        <v>0.25316</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4271</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.4</v>
+        <v>0.4328</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J36" t="n">
         <v>0.4</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" t="n">
         <v>16704</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13779,40 +13921,43 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E37" t="n">
         <v>0.7583</v>
       </c>
       <c r="F37" t="n">
-        <v>0.25167</v>
+        <v>0.25316</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4268</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.4325</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J37" t="n">
         <v>0.4</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
         <v>16704</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13831,7 +13976,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E38" t="n">
         <v>0.7529</v>
@@ -13840,31 +13985,34 @@
         <v>0.05478</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5688</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.4</v>
+        <v>0.587</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J38" t="n">
         <v>0.4</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M38" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13883,7 +14031,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E39" t="n">
         <v>0.7529</v>
@@ -13892,31 +14040,34 @@
         <v>0.05478</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5688</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.587</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J39" t="n">
         <v>0.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M39" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13935,7 +14086,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E40" t="n">
         <v>0.7583</v>
@@ -13944,31 +14095,34 @@
         <v>0.05478</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5688</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.4</v>
+        <v>0.5867</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J40" t="n">
         <v>0.4</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L40" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M40" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13987,40 +14141,43 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E41" t="n">
         <v>0.7529</v>
       </c>
       <c r="F41" t="n">
-        <v>0.11659</v>
+        <v>0.11844</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5161</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.5141</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J41" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L41" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M41" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14039,40 +14196,43 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E42" t="n">
         <v>0.7529</v>
       </c>
       <c r="F42" t="n">
-        <v>0.11659</v>
+        <v>0.11844</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5161</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.4</v>
+        <v>0.5141</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J42" t="n">
         <v>0.4</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L42" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M42" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14091,40 +14251,43 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E43" t="n">
         <v>0.7583</v>
       </c>
       <c r="F43" t="n">
-        <v>0.11659</v>
+        <v>0.11844</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5158</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.514</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J43" t="n">
         <v>0.4</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L43" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M43" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14143,40 +14306,43 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E44" t="n">
         <v>0.7529</v>
       </c>
       <c r="F44" t="n">
-        <v>0.19127</v>
+        <v>0.1924</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4391</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.4449</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J44" t="n">
         <v>0.4</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="n">
         <v>16704</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14195,40 +14361,43 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E45" t="n">
         <v>0.7529</v>
       </c>
       <c r="F45" t="n">
-        <v>0.19127</v>
+        <v>0.1924</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4391</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.4449</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J45" t="n">
         <v>0.4</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M45" t="n">
         <v>16704</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14247,40 +14416,43 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E46" t="n">
         <v>0.7583</v>
       </c>
       <c r="F46" t="n">
-        <v>0.19127</v>
+        <v>0.1924</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4389</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.4447</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J46" t="n">
         <v>0.4</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M46" t="n">
         <v>16704</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14299,7 +14471,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E47" t="n">
         <v>0.7529</v>
@@ -14308,31 +14480,34 @@
         <v>0.03748</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5723</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.5904</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J47" t="n">
         <v>0.4</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L47" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M47" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14351,7 +14526,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.6966</v>
+        <v>0.7419</v>
       </c>
       <c r="E48" t="n">
         <v>0.7529</v>
@@ -14360,31 +14535,34 @@
         <v>0.03748</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5723</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.5904</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J48" t="n">
         <v>0.4</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L48" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M48" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14403,7 +14581,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="E49" t="n">
         <v>0.7583</v>
@@ -14412,31 +14590,34 @@
         <v>0.03748</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5722</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.5901</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J49" t="n">
         <v>0.4</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L49" t="n">
-        <v>35040</v>
-      </c>
-      <c r="M49" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>16704</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14455,40 +14636,43 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E50" t="n">
         <v>0.7529</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0848</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5224</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.5206</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J50" t="n">
         <v>0.4</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L50" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M50" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14507,40 +14691,43 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.5956</v>
+        <v>0.5916</v>
       </c>
       <c r="E51" t="n">
         <v>0.7529</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0848</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5224</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.4</v>
+        <v>0.5206</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J51" t="n">
         <v>0.4</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L51" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M51" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14559,40 +14746,43 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.5896</v>
+        <v>0.586</v>
       </c>
       <c r="E52" t="n">
         <v>0.7583</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0848</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5222</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.5205</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J52" t="n">
         <v>0.4</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L52" t="n">
-        <v>16704</v>
-      </c>
-      <c r="M52" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>35040</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14611,40 +14801,43 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E53" t="n">
         <v>0.7529</v>
       </c>
       <c r="F53" t="n">
-        <v>0.14537</v>
+        <v>0.14622</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4483</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.4</v>
+        <v>0.4542</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J53" t="n">
         <v>0.4</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" t="n">
         <v>16704</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14663,40 +14856,43 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.4406</v>
+        <v>0.4556</v>
       </c>
       <c r="E54" t="n">
         <v>0.7529</v>
       </c>
       <c r="F54" t="n">
-        <v>0.14537</v>
+        <v>0.14622</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4483</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.4542</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J54" t="n">
         <v>0.4</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M54" t="n">
         <v>16704</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14715,40 +14911,43 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.4346</v>
+        <v>0.4496</v>
       </c>
       <c r="E55" t="n">
         <v>0.7583</v>
       </c>
       <c r="F55" t="n">
-        <v>0.14537</v>
+        <v>0.14622</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4481</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>marginal</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.4</v>
+        <v>0.4539</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>marginal</t>
+        </is>
       </c>
       <c r="J55" t="n">
         <v>0.4</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M55" t="n">
         <v>16704</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>per_scenario</t>
         </is>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14803,10 +15002,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="C2" t="n">
-        <v>0.022</v>
+        <v>0.02214</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -14825,10 +15024,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0209</v>
+        <v>0.0211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01608</v>
+        <v>0.01622</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -14847,10 +15046,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0159</v>
+        <v>0.016</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01177</v>
+        <v>0.01188</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -14869,10 +15068,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0121</v>
+        <v>0.0122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00861</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -14891,10 +15090,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0092</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00633</v>
+        <v>0.00639</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
